--- a/output9/【字幕】帛書版道德經。第十一章_bak.xlsx
+++ b/output9/【字幕】帛書版道德經。第十一章_bak.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1B4DD1-53BB-4C44-A2E1-11C09EA1B379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0372D53E-FF43-42E6-9253-2D84B0D91A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{871517D1-D3AE-4060-BE56-3FFC33E309BB}"/>
+    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="2" xr2:uid="{871517D1-D3AE-4060-BE56-3FFC33E309BB}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
     <sheet name="01_漢字標音" sheetId="6" r:id="rId2"/>
     <sheet name="02_計算時長" sheetId="1" r:id="rId3"/>
     <sheet name="腳本" sheetId="2" r:id="rId4"/>
-    <sheet name="海海人生" sheetId="7" r:id="rId5"/>
+    <sheet name="注音二式" sheetId="9" r:id="rId5"/>
+    <sheet name="台羅拚音" sheetId="10" r:id="rId6"/>
+    <sheet name="海海人生" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="FILE_NAME">env!$C$2</definedName>
@@ -72,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="215">
   <si>
     <t>編號</t>
   </si>
@@ -472,6 +474,9 @@
     <t>埏埴為器，當其無，有埴器之用也。</t>
   </si>
   <si>
+    <t>鑿戶牖，當其無，有室之用也。</t>
+  </si>
+  <si>
     <t>故有之以為利，無之以為用。</t>
   </si>
   <si>
@@ -566,6 +571,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>台羅拼音</t>
+  </si>
+  <si>
     <t>漢字標音</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -720,6 +728,41 @@
     <t>Tshiò-tshiò gún bô khian-kuà</t>
   </si>
   <si>
+    <t>Tō tik king. Tē si̍p it tsiong</t>
+  </si>
+  <si>
+    <t>Tō tik king. Tē si̍p it tsiong</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</t>
+  </si>
+  <si>
+    <t>Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</t>
+  </si>
+  <si>
+    <t>Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</t>
+  </si>
+  <si>
+    <t>Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kòo íu tsi í ûi lī, bô tsi í ûi īong.</t>
+  </si>
+  <si>
+    <t>Kòo íu tsi í ûi lī, bô tsi í ûi īong.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>鑿戶牖，當其無，有室之用也。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -740,26 +783,114 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>注音二式</t>
-  </si>
-  <si>
-    <t>Dor7 diek4 ging1. De7 ship8 it4 jiong1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ship4 hok4 dang5 it4 gok4, dong1 gi5 bbor5, iu2 gu1 ji1 iong7 ia2.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ian5 shit8 ui5 ki3, dong1 gi5 bbor5, iu2 shit8 ki3 ji1 iong7 ia2.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cak8 hoo7 牖, dong1 gi5 bbor5, iu2 shiek4 ji1 iong7 ia2.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Goo3 iu2 ji1 i2 ui5 li7, bbor5 ji1 i2 ui5 iong7.</t>
+    <t>《道德經。第十一章》</t>
+  </si>
+  <si>
+    <t>埏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>埴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iân</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>埏埴為器，當其無，有埴器之用也。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Si̍t</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tì</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑿戶牖，當其無，有室之用也。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>室</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Îan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>si̍t</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tsha̍k hōo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Noto Sans TC"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>牖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Charis SIL"/>
+      </rPr>
+      <t>, tong kî bô, íu sik tsi īong ía.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢文輔助系統</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阮的注音</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChhoeTaigi+
+甘字典</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sik</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ian5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -773,7 +904,7 @@
     <numFmt numFmtId="177" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
     <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="47">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1026,8 +1157,57 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Charis SemiBold"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Charis SemiBold"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Noto Sans HK"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Noto Sans HK"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="Noto Sans HK"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFC00000"/>
+      <name val="Charis SemiBold"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1108,8 +1288,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1160,6 +1352,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1177,7 +1410,7 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1369,6 +1602,53 @@
     </xf>
     <xf numFmtId="49" fontId="22" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1728,66 +2008,66 @@
   <sheetData>
     <row r="1" spans="2:3" ht="26.25">
       <c r="B1" s="51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="2:3" ht="30">
       <c r="B2" s="54" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30">
       <c r="B6" s="53" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30">
       <c r="B7" s="53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="30">
       <c r="B8" s="53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>182</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="2:3">
@@ -1826,7 +2106,8 @@
     <col min="12" max="12" width="12.875" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="13" max="16" width="14" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="49.625" style="39" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="126.75" style="39" customWidth="1"/>
+    <col min="18" max="18" width="93.5" style="39" customWidth="1"/>
+    <col min="20" max="20" width="101.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24">
@@ -1900,10 +2181,10 @@
         <v>89</v>
       </c>
       <c r="Q3" s="40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R3" s="40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34.5">
@@ -1968,10 +2249,10 @@
         <v>000</v>
       </c>
       <c r="Q4" s="41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R4" s="43" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="34.5">
@@ -2040,7 +2321,7 @@
         <v>103</v>
       </c>
       <c r="R5" s="43" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="34.5">
@@ -2109,7 +2390,7 @@
         <v>104</v>
       </c>
       <c r="R6" s="43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5">
@@ -2175,7 +2456,7 @@
         <v>000</v>
       </c>
       <c r="Q7" s="41" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="R7" s="43" t="s">
         <v>186</v>
@@ -2244,10 +2525,10 @@
         <v>000</v>
       </c>
       <c r="Q8" s="41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R8" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="24">
@@ -2323,8 +2604,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20734DEE-CDEB-4D52-893F-33C0A347653E}">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="27"/>
   <cols>
     <col min="1" max="1" width="7" style="3" customWidth="1"/>
     <col min="2" max="3" width="14" style="3" customWidth="1"/>
@@ -2332,6 +2613,7 @@
     <col min="5" max="6" width="14" style="3" customWidth="1"/>
     <col min="7" max="8" width="49.625" style="7" customWidth="1"/>
     <col min="9" max="9" width="31.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="63.875" style="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30">
@@ -2354,10 +2636,10 @@
         <v>100</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H1" s="32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I1" s="32" t="s">
         <v>3</v>
@@ -2392,14 +2674,19 @@
       </c>
       <c r="H2" s="64" t="str">
         <f>'01_漢字標音'!R4</f>
-        <v>Dor7 diek4 ging1. De7 ship8 it4 jiong1</v>
+        <v>Tō tik king. Tē si̍p it tsiong</v>
       </c>
       <c r="I2" s="46" t="str">
         <f>A2&amp;CHAR(10)&amp;B2&amp;" --&gt; "&amp;C2&amp;CHAR(10)&amp;G2&amp;CHAR(10)&amp;H2</f>
         <v>1
 00:00:00,000 --&gt; 00:00:07,000
 《道德經。第十一章》
-Dor7 diek4 ging1. De7 ship8 it4 jiong1</v>
+Tō tik king. Tē si̍p it tsiong</v>
+      </c>
+      <c r="K2" s="66" t="str">
+        <f>_xlfn.CONCAT(G2,CHAR(10),H2)</f>
+        <v>《道德經。第十一章》
+Tō tik king. Tē si̍p it tsiong</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="75">
@@ -2407,7 +2694,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C3" s="47" t="str">
         <f t="shared" ref="C3:C5" si="0">B4</f>
@@ -2431,14 +2718,19 @@
       </c>
       <c r="H3" s="64" t="str">
         <f>'01_漢字標音'!R5</f>
-        <v>Ship4 hok4 dang5 it4 gok4, dong1 gi5 bbor5, iu2 gu1 ji1 iong7 ia2.</v>
+        <v>Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</v>
       </c>
       <c r="I3" s="46" t="str">
         <f t="shared" ref="I3:I6" si="4">A3&amp;CHAR(10)&amp;B3&amp;" --&gt; "&amp;C3&amp;CHAR(10)&amp;G3&amp;CHAR(10)&amp;H3</f>
         <v>2
 00:00:07,000 --&gt; 00:00:20,000
 卅輻同一轂，當其無，有車之用也。
-Ship4 hok4 dang5 it4 gok4, dong1 gi5 bbor5, iu2 gu1 ji1 iong7 ia2.</v>
+Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</v>
+      </c>
+      <c r="K3" s="66" t="str">
+        <f t="shared" ref="K3:K6" si="5">_xlfn.CONCAT(G3, " ",CHAR(10),H3)</f>
+        <v>卅輻同一轂，當其無，有車之用也。 
+Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="75">
@@ -2446,7 +2738,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C4" s="47" t="str">
         <f t="shared" si="0"/>
@@ -2470,14 +2762,19 @@
       </c>
       <c r="H4" s="64" t="str">
         <f>'01_漢字標音'!R6</f>
-        <v>Ian5 shit8 ui5 ki3, dong1 gi5 bbor5, iu2 shit8 ki3 ji1 iong7 ia2.</v>
+        <v>Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</v>
       </c>
       <c r="I4" s="46" t="str">
         <f t="shared" si="4"/>
         <v>3
 00:00:20,000 --&gt; 00:00:33,000
 埏埴為器，當其無，有埴器之用也。
-Ian5 shit8 ui5 ki3, dong1 gi5 bbor5, iu2 shit8 ki3 ji1 iong7 ia2.</v>
+Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</v>
+      </c>
+      <c r="K4" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>埏埴為器，當其無，有埴器之用也。 
+Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="75">
@@ -2485,7 +2782,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -2509,14 +2806,19 @@
       </c>
       <c r="H5" s="64" t="str">
         <f>'01_漢字標音'!R7</f>
-        <v>Cak8 hoo7 牖, dong1 gi5 bbor5, iu2 shiek4 ji1 iong7 ia2.</v>
+        <v>Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</v>
       </c>
       <c r="I5" s="46" t="str">
         <f t="shared" si="4"/>
         <v>4
 00:00:33,000 --&gt; 00:00:43,000
 鑿戶牖，當其無，有室之用也。
-Cak8 hoo7 牖, dong1 gi5 bbor5, iu2 shiek4 ji1 iong7 ia2.</v>
+Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</v>
+      </c>
+      <c r="K5" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>鑿戶牖，當其無，有室之用也。 
+Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="60">
@@ -2524,7 +2826,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C6" s="50" t="str">
         <f>B7</f>
@@ -2548,14 +2850,19 @@
       </c>
       <c r="H6" s="64" t="str">
         <f>'01_漢字標音'!R8</f>
-        <v>Goo3 iu2 ji1 i2 ui5 li7, bbor5 ji1 i2 ui5 iong7.</v>
+        <v>Kòo íu tsi í ûi lī, bô tsi í ûi īong.</v>
       </c>
       <c r="I6" s="46" t="str">
         <f t="shared" si="4"/>
         <v>5
 00:00:43,000 --&gt; 00:01:00,000
 故有之以為利，無之以為用。
-Goo3 iu2 ji1 i2 ui5 li7, bbor5 ji1 i2 ui5 iong7.</v>
+Kòo íu tsi í ûi lī, bô tsi í ûi īong.</v>
+      </c>
+      <c r="K6" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>故有之以為利，無之以為用。 
+Kòo íu tsi í ûi lī, bô tsi í ûi īong.</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2563,13 +2870,115 @@
         <v>18</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="67"/>
       <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" ht="69">
+      <c r="G8" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" s="64" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="69">
+      <c r="B9" s="73" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" s="72"/>
+      <c r="G9" s="69" t="s">
+        <v>198</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="40.5">
+      <c r="B10" s="76" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="74" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="78" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="F10" s="68"/>
+      <c r="G10" s="70" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="40.5">
+      <c r="B11" s="76" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" s="78" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="77"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="40.5">
+      <c r="B12" s="79"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="81" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="81"/>
+      <c r="F12" s="68"/>
+    </row>
+    <row r="13" spans="1:12" ht="40.5">
+      <c r="B13" s="79" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="80" t="s">
+        <v>213</v>
+      </c>
+      <c r="E13" s="80" t="s">
+        <v>209</v>
+      </c>
+      <c r="F13" s="68"/>
+      <c r="G13" s="70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="40.5">
+      <c r="F14" s="68"/>
+      <c r="G14" s="70"/>
+    </row>
+    <row r="15" spans="1:12" ht="40.5">
+      <c r="F15" s="68"/>
+      <c r="G15" s="70"/>
+    </row>
+    <row r="16" spans="1:12" ht="40.5">
+      <c r="F16" s="68"/>
+      <c r="G16" s="70"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2655,6 +3064,534 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9311C8BE-DA44-4271-8ADE-E0200831BF1B}">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="7" style="3" customWidth="1"/>
+    <col min="2" max="3" width="14" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="3" customWidth="1"/>
+    <col min="5" max="6" width="14" style="3" customWidth="1"/>
+    <col min="7" max="8" width="49.625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="31.5" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="30">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="60">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="47" t="str">
+        <f>B3</f>
+        <v>00:00:07,000</v>
+      </c>
+      <c r="D2" s="36">
+        <f>F2-E2</f>
+        <v>7000</v>
+      </c>
+      <c r="E2" s="37">
+        <f xml:space="preserve"> (LEFT($B2,2)*3600 + MID($B2,4,2)*60 + MID($B2,7,2))*1000 + RIGHT($B2,3)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="37">
+        <f xml:space="preserve"> (LEFT($C2,2)*3600 + MID($C2,4,2)*60 + MID($C2,7,2))*1000 + RIGHT($C2,3)</f>
+        <v>7000</v>
+      </c>
+      <c r="G2" s="44" t="str">
+        <f>'01_漢字標音'!Q4</f>
+        <v>《道德經。第十一章》</v>
+      </c>
+      <c r="H2" s="64" t="str">
+        <f>'01_漢字標音'!R4</f>
+        <v>Tō tik king. Tē si̍p it tsiong</v>
+      </c>
+      <c r="I2" s="46" t="str">
+        <f>A2&amp;CHAR(10)&amp;B2&amp;" --&gt; "&amp;C2&amp;CHAR(10)&amp;G2&amp;CHAR(10)&amp;H2</f>
+        <v>1
+00:00:00,000 --&gt; 00:00:07,000
+《道德經。第十一章》
+Tō tik king. Tē si̍p it tsiong</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="75">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="47" t="str">
+        <f t="shared" ref="C3:C5" si="0">B4</f>
+        <v>00:00:20,000</v>
+      </c>
+      <c r="D3" s="36">
+        <f t="shared" ref="D3:D6" si="1">F3-E3</f>
+        <v>13000</v>
+      </c>
+      <c r="E3" s="37">
+        <f t="shared" ref="E3:E6" si="2" xml:space="preserve"> (LEFT($B3,2)*3600 + MID($B3,4,2)*60 + MID($B3,7,2))*1000 + RIGHT($B3,3)</f>
+        <v>7000</v>
+      </c>
+      <c r="F3" s="37">
+        <f t="shared" ref="F3:F6" si="3" xml:space="preserve"> (LEFT($C3,2)*3600 + MID($C3,4,2)*60 + MID($C3,7,2))*1000 + RIGHT($C3,3)</f>
+        <v>20000</v>
+      </c>
+      <c r="G3" s="44" t="str">
+        <f>'01_漢字標音'!Q5</f>
+        <v>卅輻同一轂，當其無，有車之用也。</v>
+      </c>
+      <c r="H3" s="64" t="str">
+        <f>'01_漢字標音'!R5</f>
+        <v>Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</v>
+      </c>
+      <c r="I3" s="46" t="str">
+        <f t="shared" ref="I3:I6" si="4">A3&amp;CHAR(10)&amp;B3&amp;" --&gt; "&amp;C3&amp;CHAR(10)&amp;G3&amp;CHAR(10)&amp;H3</f>
+        <v>2
+00:00:07,000 --&gt; 00:00:20,000
+卅輻同一轂，當其無，有車之用也。
+Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00:00:33,000</v>
+      </c>
+      <c r="D4" s="36">
+        <f t="shared" si="1"/>
+        <v>13000</v>
+      </c>
+      <c r="E4" s="37">
+        <f t="shared" si="2"/>
+        <v>20000</v>
+      </c>
+      <c r="F4" s="37">
+        <f t="shared" si="3"/>
+        <v>33000</v>
+      </c>
+      <c r="G4" s="44" t="str">
+        <f>'01_漢字標音'!Q6</f>
+        <v>埏埴為器，當其無，有埴器之用也。</v>
+      </c>
+      <c r="H4" s="64" t="str">
+        <f>'01_漢字標音'!R6</f>
+        <v>Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</v>
+      </c>
+      <c r="I4" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>3
+00:00:20,000 --&gt; 00:00:33,000
+埏埴為器，當其無，有埴器之用也。
+Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="75">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00:00:43,000</v>
+      </c>
+      <c r="D5" s="36">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="E5" s="37">
+        <f t="shared" si="2"/>
+        <v>33000</v>
+      </c>
+      <c r="F5" s="37">
+        <f t="shared" si="3"/>
+        <v>43000</v>
+      </c>
+      <c r="G5" s="44" t="str">
+        <f>'01_漢字標音'!Q7</f>
+        <v>鑿戶牖，當其無，有室之用也。</v>
+      </c>
+      <c r="H5" s="64" t="str">
+        <f>'01_漢字標音'!R7</f>
+        <v>Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</v>
+      </c>
+      <c r="I5" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>4
+00:00:33,000 --&gt; 00:00:43,000
+鑿戶牖，當其無，有室之用也。
+Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="60">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="50" t="str">
+        <f>B7</f>
+        <v>00:01:00,000</v>
+      </c>
+      <c r="D6" s="36">
+        <f t="shared" si="1"/>
+        <v>17000</v>
+      </c>
+      <c r="E6" s="37">
+        <f t="shared" si="2"/>
+        <v>43000</v>
+      </c>
+      <c r="F6" s="37">
+        <f t="shared" si="3"/>
+        <v>60000</v>
+      </c>
+      <c r="G6" s="44" t="str">
+        <f>'01_漢字標音'!Q8</f>
+        <v>故有之以為利，無之以為用。</v>
+      </c>
+      <c r="H6" s="64" t="str">
+        <f>'01_漢字標音'!R8</f>
+        <v>Kòo íu tsi í ûi lī, bô tsi í ûi īong.</v>
+      </c>
+      <c r="I6" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>5
+00:00:43,000 --&gt; 00:01:00,000
+故有之以為利，無之以為用。
+Kòo íu tsi í ûi lī, bô tsi í ûi īong.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB9FCEF-2652-41D6-9004-DE79BFCBFB59}">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="27"/>
+  <cols>
+    <col min="1" max="1" width="7" style="3" customWidth="1"/>
+    <col min="2" max="3" width="14" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="3" customWidth="1"/>
+    <col min="5" max="6" width="14" style="3" customWidth="1"/>
+    <col min="7" max="8" width="49.625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="31.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="63.875" style="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="30">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="60">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="47" t="str">
+        <f>B3</f>
+        <v>00:00:07,000</v>
+      </c>
+      <c r="D2" s="36">
+        <f>F2-E2</f>
+        <v>7000</v>
+      </c>
+      <c r="E2" s="37">
+        <f xml:space="preserve"> (LEFT($B2,2)*3600 + MID($B2,4,2)*60 + MID($B2,7,2))*1000 + RIGHT($B2,3)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="37">
+        <f xml:space="preserve"> (LEFT($C2,2)*3600 + MID($C2,4,2)*60 + MID($C2,7,2))*1000 + RIGHT($C2,3)</f>
+        <v>7000</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2" s="46" t="str">
+        <f>A2&amp;CHAR(10)&amp;B2&amp;" --&gt; "&amp;C2&amp;CHAR(10)&amp;G2&amp;CHAR(10)&amp;H2</f>
+        <v>1
+00:00:00,000 --&gt; 00:00:07,000
+《道德經。第十一章》
+Tō tik king. Tē si̍p it tsiong</v>
+      </c>
+      <c r="K2" s="66" t="str">
+        <f>_xlfn.CONCAT(G2,CHAR(10),H2)</f>
+        <v>《道德經。第十一章》
+Tō tik king. Tē si̍p it tsiong</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="75">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="47" t="str">
+        <f t="shared" ref="C3:C5" si="0">B4</f>
+        <v>00:00:20,000</v>
+      </c>
+      <c r="D3" s="36">
+        <f t="shared" ref="D3:D6" si="1">F3-E3</f>
+        <v>13000</v>
+      </c>
+      <c r="E3" s="37">
+        <f t="shared" ref="E3:E6" si="2" xml:space="preserve"> (LEFT($B3,2)*3600 + MID($B3,4,2)*60 + MID($B3,7,2))*1000 + RIGHT($B3,3)</f>
+        <v>7000</v>
+      </c>
+      <c r="F3" s="37">
+        <f t="shared" ref="F3:F6" si="3" xml:space="preserve"> (LEFT($C3,2)*3600 + MID($C3,4,2)*60 + MID($C3,7,2))*1000 + RIGHT($C3,3)</f>
+        <v>20000</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="46" t="str">
+        <f t="shared" ref="I3:I6" si="4">A3&amp;CHAR(10)&amp;B3&amp;" --&gt; "&amp;C3&amp;CHAR(10)&amp;G3&amp;CHAR(10)&amp;H3</f>
+        <v>2
+00:00:07,000 --&gt; 00:00:20,000
+卅輻同一轂，當其無，有車之用也。
+Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</v>
+      </c>
+      <c r="K3" s="66" t="str">
+        <f t="shared" ref="K3:K6" si="5">_xlfn.CONCAT(G3, " ",CHAR(10),H3)</f>
+        <v>卅輻同一轂，當其無，有車之用也。 
+Sip hok tâng it kok, tong kî bô, íu ku tsi īong ía.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00:00:33,000</v>
+      </c>
+      <c r="D4" s="36">
+        <f t="shared" si="1"/>
+        <v>13000</v>
+      </c>
+      <c r="E4" s="37">
+        <f t="shared" si="2"/>
+        <v>20000</v>
+      </c>
+      <c r="F4" s="37">
+        <f t="shared" si="3"/>
+        <v>33000</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="64" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>3
+00:00:20,000 --&gt; 00:00:33,000
+埏埴為器，當其無，有埴器之用也。
+Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</v>
+      </c>
+      <c r="K4" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>埏埴為器，當其無，有埴器之用也。 
+Îan si̍t ûi khì, tong kî bô, íu si̍t khì tsi īong ía.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="75">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00:00:43,000</v>
+      </c>
+      <c r="D5" s="36">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="E5" s="37">
+        <f t="shared" si="2"/>
+        <v>33000</v>
+      </c>
+      <c r="F5" s="37">
+        <f t="shared" si="3"/>
+        <v>43000</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="I5" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>4
+00:00:33,000 --&gt; 00:00:43,000
+鑿戶牖，當其無，有室之用也。
+Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</v>
+      </c>
+      <c r="K5" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>鑿戶牖，當其無，有室之用也。 
+Tsha̍k hōo 牖, tong kî bô, íu sik tsi īong ía.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="60">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="50" t="str">
+        <f>B7</f>
+        <v>00:01:00,000</v>
+      </c>
+      <c r="D6" s="36">
+        <f t="shared" si="1"/>
+        <v>17000</v>
+      </c>
+      <c r="E6" s="37">
+        <f t="shared" si="2"/>
+        <v>43000</v>
+      </c>
+      <c r="F6" s="37">
+        <f t="shared" si="3"/>
+        <v>60000</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>5
+00:00:43,000 --&gt; 00:01:00,000
+故有之以為利，無之以為用。
+Kòo íu tsi í ûi lī, bô tsi í ûi īong.</v>
+      </c>
+      <c r="K6" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>故有之以為利，無之以為用。 
+Kòo íu tsi í ûi lī, bô tsi í ûi īong.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D062096F-C75D-4513-A9FD-88B21B160D1B}">
   <dimension ref="A1:L63"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -2720,10 +3657,10 @@
         <v>48000</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I2" s="46" t="str">
         <f>A2&amp;CHAR(10)&amp;B2&amp;" --&gt; "&amp;C2&amp;CHAR(10)&amp;G2&amp;CHAR(10)&amp;H2</f>
@@ -2757,10 +3694,10 @@
         <v>50324</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H3" s="45" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I3" s="46" t="str">
         <f t="shared" ref="I3:I62" si="4">A3&amp;CHAR(10)&amp;B3&amp;" --&gt; "&amp;C3&amp;CHAR(10)&amp;G3&amp;CHAR(10)&amp;H3</f>
@@ -2794,10 +3731,10 @@
         <v>53920</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H4" s="45" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I4" s="46" t="str">
         <f t="shared" si="4"/>
@@ -2831,10 +3768,10 @@
         <v>55000</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H5" s="45" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I5" s="46" t="str">
         <f t="shared" si="4"/>
@@ -2868,10 +3805,10 @@
         <v>59000</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H6" s="45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I6" s="46" t="str">
         <f t="shared" si="4"/>
@@ -2905,10 +3842,10 @@
         <v>61917</v>
       </c>
       <c r="G7" s="44" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I7" s="46" t="str">
         <f t="shared" si="4"/>
@@ -2942,10 +3879,10 @@
         <v>64001</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H8" s="45" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I8" s="46" t="str">
         <f t="shared" si="4"/>
@@ -2979,10 +3916,10 @@
         <v>67003</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H9" s="45" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I9" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3016,10 +3953,10 @@
         <v>71006</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H10" s="45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I10" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3053,10 +3990,10 @@
         <v>73010</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H11" s="45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I11" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3090,10 +4027,10 @@
         <v>76015</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H12" s="45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I12" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3127,10 +4064,10 @@
         <v>78021</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H13" s="45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I13" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3164,10 +4101,10 @@
         <v>82028</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H14" s="45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I14" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3201,10 +4138,10 @@
         <v>84036</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H15" s="45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I15" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3238,10 +4175,10 @@
         <v>88045</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H16" s="45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I16" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3275,10 +4212,10 @@
         <v>89055</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H17" s="45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I17" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3312,10 +4249,10 @@
         <v>94066</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H18" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I18" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3349,10 +4286,10 @@
         <v>96078</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H19" s="45" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I19" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3386,10 +4323,10 @@
         <v>99069</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H20" s="45" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I20" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3423,10 +4360,10 @@
         <v>101712</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H21" s="45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I21" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3460,10 +4397,10 @@
         <v>105120</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H22" s="45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I22" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3497,10 +4434,10 @@
         <v>108136</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H23" s="45" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I23" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3534,10 +4471,10 @@
         <v>110153</v>
       </c>
       <c r="G24" s="44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H24" s="45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I24" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3571,10 +4508,10 @@
         <v>112171</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H25" s="45" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I25" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3608,10 +4545,10 @@
         <v>116190</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I26" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3645,10 +4582,10 @@
         <v>118210</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H27" s="45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I27" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3682,10 +4619,10 @@
         <v>122231</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H28" s="45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I28" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3719,10 +4656,10 @@
         <v>124253</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H29" s="45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I29" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3756,10 +4693,10 @@
         <v>128276</v>
       </c>
       <c r="G30" s="44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H30" s="45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I30" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3793,10 +4730,10 @@
         <v>130300</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H31" s="45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I31" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3830,10 +4767,10 @@
         <v>133325</v>
       </c>
       <c r="G32" s="44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H32" s="45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I32" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3867,10 +4804,10 @@
         <v>134351</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H33" s="45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I33" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3903,10 +4840,10 @@
         <v>142000</v>
       </c>
       <c r="G34" s="44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H34" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I34" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3940,10 +4877,10 @@
         <v>170406</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H35" s="45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I35" s="46" t="str">
         <f t="shared" si="4"/>
@@ -3977,10 +4914,10 @@
         <v>173435</v>
       </c>
       <c r="G36" s="44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H36" s="45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I36" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4014,10 +4951,10 @@
         <v>176000</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H37" s="45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I37" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4051,10 +4988,10 @@
         <v>179000</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H38" s="45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I38" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4088,10 +5025,10 @@
         <v>181000</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H39" s="45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I39" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4125,10 +5062,10 @@
         <v>184000</v>
       </c>
       <c r="G40" s="44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H40" s="45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I40" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4162,10 +5099,10 @@
         <v>186000</v>
       </c>
       <c r="G41" s="44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H41" s="45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I41" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4199,10 +5136,10 @@
         <v>190000</v>
       </c>
       <c r="G42" s="44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H42" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I42" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4236,10 +5173,10 @@
         <v>193000</v>
       </c>
       <c r="G43" s="44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H43" s="45" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I43" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4273,10 +5210,10 @@
         <v>196000</v>
       </c>
       <c r="G44" s="44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H44" s="45" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I44" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4310,10 +5247,10 @@
         <v>198000</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H45" s="45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I45" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4347,10 +5284,10 @@
         <v>202000</v>
       </c>
       <c r="G46" s="44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H46" s="45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I46" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4384,10 +5321,10 @@
         <v>205000</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H47" s="45" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I47" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4421,10 +5358,10 @@
         <v>207000</v>
       </c>
       <c r="G48" s="44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H48" s="45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I48" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4458,10 +5395,10 @@
         <v>209000</v>
       </c>
       <c r="G49" s="44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H49" s="45" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I49" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4495,10 +5432,10 @@
         <v>213000</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H50" s="45" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I50" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4532,10 +5469,10 @@
         <v>216000</v>
       </c>
       <c r="G51" s="44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H51" s="45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I51" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4569,10 +5506,10 @@
         <v>219000</v>
       </c>
       <c r="G52" s="44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H52" s="45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I52" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4606,10 +5543,10 @@
         <v>221000</v>
       </c>
       <c r="G53" s="44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H53" s="45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I53" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4643,10 +5580,10 @@
         <v>225000</v>
       </c>
       <c r="G54" s="44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H54" s="45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I54" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4680,10 +5617,10 @@
         <v>227000</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H55" s="45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I55" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4717,10 +5654,10 @@
         <v>230000</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H56" s="45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I56" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4754,10 +5691,10 @@
         <v>231000</v>
       </c>
       <c r="G57" s="44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H57" s="45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I57" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4791,10 +5728,10 @@
         <v>236000</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H58" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I58" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4828,10 +5765,10 @@
         <v>237000</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H59" s="45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I59" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4865,10 +5802,10 @@
         <v>241000</v>
       </c>
       <c r="G60" s="44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H60" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I60" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4902,10 +5839,10 @@
         <v>243000</v>
       </c>
       <c r="G61" s="44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H61" s="45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I61" s="46" t="str">
         <f t="shared" si="4"/>
@@ -4939,10 +5876,10 @@
         <v>254000</v>
       </c>
       <c r="G62" s="44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H62" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I62" s="46" t="str">
         <f t="shared" si="4"/>

--- a/output9/【字幕】帛書版道德經。第十一章_bak.xlsx
+++ b/output9/【字幕】帛書版道德經。第十一章_bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0372D53E-FF43-42E6-9253-2D84B0D91A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88870EDB-010A-42C6-9734-4129B4D48A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="2" xr2:uid="{871517D1-D3AE-4060-BE56-3FFC33E309BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{871517D1-D3AE-4060-BE56-3FFC33E309BB}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
